--- a/published/01_Equity_SouthAfrica.xlsx
+++ b/published/01_Equity_SouthAfrica.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,19 +60,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/published/01_Equity_SouthAfrica.xlsx
+++ b/published/01_Equity_SouthAfrica.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,13 +63,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/published/01_Equity_SouthAfrica.xlsx
+++ b/published/01_Equity_SouthAfrica.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SA_Focus" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$L$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,20 +444,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="33" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -581,8 +581,224 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4Di Capital</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Justin Stanford</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/justinstanford</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[4dicapital.com](https://4dicapital.com)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Tech / Fintech</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.4dicapital.com/team</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Knife Capital</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Keet van Zyl</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/keetvanzyl</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[knifecap.com](https://knifecap.com)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Tech / Emerging Markets</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Series A-B</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knifecap.com/team</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kalon Venture Partners</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Clive Butkow</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clivebutkow</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[kalonvp.com](https://kalonvp.com)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Tech / AI / SaaS</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://kalonvp.com/team</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Savant</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Nick Allen</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nick-allen-2b1b2a</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[savant.co.za](https://savant.co.za)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>DeepTech / Tech</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>VC / Incubator</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://savant.co.za/team</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/01_Equity_SouthAfrica.xlsx
+++ b/published/01_Equity_SouthAfrica.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,19 +60,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -526,23 +517,23 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CRE Venture Capital</t>
+          <t>4Di Capital</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pardon Makumbe</t>
+          <t>Justin Stanford</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pardonmakumbe</t>
+          <t>https://www.linkedin.com/in/justinstanford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[cre.vc](https://cre.vc)</t>
+          <t>[4dicapital.com](https://4dicapital.com)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -557,7 +548,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tech / Emerging Markets</t>
+          <t>Tech / Fintech</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -572,35 +563,31 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://cre.vc)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa focus</t>
-        </is>
-      </c>
+          <t>https://www.4dicapital.com/team</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4Di Capital</t>
+          <t>Knife Capital</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Justin Stanford</t>
+          <t>Keet van Zyl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/justinstanford</t>
+          <t>https://www.linkedin.com/in/keetvanzyl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[4dicapital.com](https://4dicapital.com)</t>
+          <t>[knifecap.com](https://knifecap.com)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -615,7 +602,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tech / Fintech</t>
+          <t>Tech / Emerging Markets</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -625,12 +612,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Seed / Series A</t>
+          <t>Series A-B</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.4dicapital.com/team</t>
+          <t>https://www.knifecap.com/team</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -638,23 +625,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Knife Capital</t>
+          <t>Kalon Venture Partners</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Keet van Zyl</t>
+          <t>Clive Butkow</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/keetvanzyl</t>
+          <t>https://www.linkedin.com/in/clivebutkow</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[knifecap.com](https://knifecap.com)</t>
+          <t>[kalonvp.com](https://kalonvp.com)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -669,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tech / Emerging Markets</t>
+          <t>Tech / AI / SaaS</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -679,12 +666,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Series A-B</t>
+          <t>Seed / Series A</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>https://www.knifecap.com/team</t>
+          <t>https://kalonvp.com/team</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -692,23 +679,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kalon Venture Partners</t>
+          <t>Savant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clive Butkow</t>
+          <t>Nick Allen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/clivebutkow</t>
+          <t>https://www.linkedin.com/in/nick-allen-2b1b2a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[kalonvp.com](https://kalonvp.com)</t>
+          <t>[savant.co.za](https://savant.co.za)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -723,22 +710,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tech / AI / SaaS</t>
+          <t>DeepTech / Tech</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>VC / Incubator</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Seed / Series A</t>
+          <t>Seed</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://kalonvp.com/team</t>
+          <t>https://savant.co.za/team</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -746,23 +733,23 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>CRE Venture Capital</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Nick Allen</t>
+          <t>Pardon Makumbe</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nick-allen-2b1b2a</t>
+          <t>https://www.linkedin.com/in/pardonmakumbe</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[savant.co.za](https://savant.co.za)</t>
+          <t>[cre.vc](https://cre.vc)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -777,25 +764,29 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>DeepTech / Tech</t>
+          <t>Tech / Emerging Markets</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>VC / Incubator</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Seed / Series A</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://savant.co.za/team</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>[Team/Contact](https://cre.vc)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa focus</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L6"/>

--- a/published/01_Equity_SouthAfrica.xlsx
+++ b/published/01_Equity_SouthAfrica.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SA_Focus" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -448,8 +448,7 @@
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,11 +504,6 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Source / Verification</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -561,12 +555,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.4dicapital.com/team</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -615,12 +604,7 @@
           <t>Series A-B</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://www.knifecap.com/team</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -669,12 +653,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>https://kalonvp.com/team</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -723,12 +702,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://savant.co.za/team</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -779,17 +753,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://cre.vc)</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
           <t>Sub-Saharan Africa focus</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/01_Equity_SouthAfrica.xlsx
+++ b/published/01_Equity_SouthAfrica.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SA_Focus" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,19 +60,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -457,8 +448,7 @@
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,11 +504,6 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Source / Verification</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -526,23 +511,23 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CRE Venture Capital</t>
+          <t>4Di Capital</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pardon Makumbe</t>
+          <t>Justin Stanford</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pardonmakumbe</t>
+          <t>https://www.linkedin.com/in/justinstanford</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>[cre.vc](https://cre.vc)</t>
+          <t>[4dicapital.com](https://4dicapital.com)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -557,7 +542,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tech / Emerging Markets</t>
+          <t>Tech / Fintech</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -570,37 +555,28 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cre.vc)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Sub-Saharan Africa focus</t>
-        </is>
-      </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4Di Capital</t>
+          <t>Knife Capital</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Justin Stanford</t>
+          <t>Keet van Zyl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/justinstanford</t>
+          <t>https://www.linkedin.com/in/keetvanzyl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[4dicapital.com](https://4dicapital.com)</t>
+          <t>[knifecap.com](https://knifecap.com)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -615,7 +591,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tech / Fintech</t>
+          <t>Tech / Emerging Markets</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -625,36 +601,31 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Seed / Series A</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://www.4dicapital.com/team</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Series A-B</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Knife Capital</t>
+          <t>Kalon Venture Partners</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Keet van Zyl</t>
+          <t>Clive Butkow</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/keetvanzyl</t>
+          <t>https://www.linkedin.com/in/clivebutkow</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>[knifecap.com](https://knifecap.com)</t>
+          <t>[kalonvp.com](https://kalonvp.com)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -669,7 +640,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tech / Emerging Markets</t>
+          <t>Tech / AI / SaaS</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -679,36 +650,31 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Series A-B</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.knifecap.com/team</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kalon Venture Partners</t>
+          <t>Savant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clive Butkow</t>
+          <t>Nick Allen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/clivebutkow</t>
+          <t>https://www.linkedin.com/in/nick-allen-2b1b2a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[kalonvp.com](https://kalonvp.com)</t>
+          <t>[savant.co.za](https://savant.co.za)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -723,46 +689,41 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tech / AI / SaaS</t>
+          <t>DeepTech / Tech</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>VC / Incubator</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Seed / Series A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://kalonvp.com/team</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Savant</t>
+          <t>CRE Venture Capital</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Nick Allen</t>
+          <t>Pardon Makumbe</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nick-allen-2b1b2a</t>
+          <t>https://www.linkedin.com/in/pardonmakumbe</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>[savant.co.za](https://savant.co.za)</t>
+          <t>[cre.vc](https://cre.vc)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -777,28 +738,27 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>DeepTech / Tech</t>
+          <t>Tech / Emerging Markets</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>VC / Incubator</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Seed / Series A</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://savant.co.za/team</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>Sub-Saharan Africa focus</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/01_Equity_SouthAfrica.xlsx
+++ b/published/01_Equity_SouthAfrica.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SA_Focus" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SA_Focus'!$A$1:$L$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,13 +63,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -435,330 +444,351 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Organization Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Contact Person</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Territory</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Funder Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Funding Type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>4Di Capital</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Justin Stanford</t>
+          <t>CRE Venture Capital</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/justinstanford</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>[4dicapital.com](https://4dicapital.com)</t>
-        </is>
-      </c>
+          <t>Pardon Makumbe</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pardonmakumbe</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>[cre.vc](https://cre.vc)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Tech / Fintech</t>
-        </is>
-      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Tech / Emerging Markets</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>VC</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Sub-Saharan Africa focus</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Knife Capital</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Keet van Zyl</t>
+          <t>4Di Capital</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/keetvanzyl</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[knifecap.com](https://knifecap.com)</t>
-        </is>
-      </c>
+          <t>Justin Stanford</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/justinstanford</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
+          <t>[4dicapital.com](https://4dicapital.com)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Tech / Emerging Markets</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Tech / Fintech</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>VC</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Series A-B</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Kalon Venture Partners</t>
-        </is>
+      <c r="A4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Clive Butkow</t>
+          <t>Knife Capital</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/clivebutkow</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>[kalonvp.com](https://kalonvp.com)</t>
-        </is>
-      </c>
+          <t>Keet van Zyl</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/keetvanzyl</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>[knifecap.com](https://knifecap.com)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Tech / AI / SaaS</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>Tech / Emerging Markets</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>VC</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Seed / Series A</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Series A-B</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Savant</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nick Allen</t>
+          <t>Kalon Venture Partners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nick-allen-2b1b2a</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[savant.co.za](https://savant.co.za)</t>
-        </is>
-      </c>
+          <t>Clive Butkow</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/clivebutkow</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
+          <t>[kalonvp.com](https://kalonvp.com)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>DeepTech / Tech</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VC / Incubator</t>
+          <t>Tech / AI / SaaS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Seed</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Seed / Series A</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CRE Venture Capital</t>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Pardon Makumbe</t>
+          <t>Savant</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pardonmakumbe</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>[cre.vc](https://cre.vc)</t>
-        </is>
-      </c>
+          <t>Nick Allen</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nick-allen-2b1b2a</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>[savant.co.za](https://savant.co.za)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Tech / Emerging Markets</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>DeepTech / Tech</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Seed / Series A</t>
+          <t>VC / Incubator</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Sub-Saharan Africa focus</t>
-        </is>
-      </c>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>